--- a/Mod_Korean/Lang/KR/Game/Job.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Job.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">warrior</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.338 Patch 2</t>
+    <t xml:space="preserve">EA 23.352</t>
   </si>
   <si>
     <t xml:space="preserve">戦士</t>

--- a/Mod_Korean/Lang/KR/Game/Job.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Job.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">warrior</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.352</t>
+    <t xml:space="preserve">EA 23.355</t>
   </si>
   <si>
     <t xml:space="preserve">戦士</t>
